--- a/tables/FST_V2.xlsx
+++ b/tables/FST_V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\woodbison\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AFD6BF-B3EB-408B-AAFF-E36B049D04A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CEAF65-A87B-4536-8615-2FA33CFC2417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="22">
   <si>
     <t>WENT</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>NORD</t>
+  </si>
+  <si>
+    <t>n/a</t>
   </si>
 </sst>
 </file>
@@ -171,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -203,20 +206,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -232,6 +226,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,7 +527,22 @@
     <col min="12" max="12" width="4.88671875" style="6" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="6"/>
+    <col min="15" max="16" width="8.88671875" style="6"/>
+    <col min="17" max="17" width="7" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7" style="6" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.3">
@@ -670,1047 +685,1056 @@
       <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="Q3" s="19" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="Q3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18"/>
+      <c r="Y3" s="18"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="19"/>
+      <c r="AH3" s="19"/>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>-3.1429596454029098E-3</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="Q4" s="19" t="s">
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="Q4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="12">
+      <c r="R4" s="11">
         <v>3.5396784528437799E-3</v>
       </c>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="13"/>
-      <c r="AF4" s="13"/>
-      <c r="AG4" s="13"/>
-      <c r="AH4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="14"/>
+      <c r="AF4" s="14"/>
+      <c r="AG4" s="14"/>
+      <c r="AH4" s="14"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>4.0664919161560601E-3</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>9.4264103609615207E-3</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="Q5" s="19" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="Q5" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="R5" s="12">
+      <c r="R5" s="13">
         <v>2.1543286913761599E-2</v>
       </c>
-      <c r="S5" s="12">
+      <c r="S5" s="13">
         <v>9.2899078691363202E-3</v>
       </c>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-      <c r="AE5" s="13"/>
-      <c r="AF5" s="13"/>
-      <c r="AG5" s="13"/>
-      <c r="AH5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="11">
         <v>8.0149455052172108E-3</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="13">
         <v>1.04494749251742E-2</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="13">
         <v>1.8235582050627398E-2</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="Q6" s="19" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="Q6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="13">
         <v>1.7830872521447601E-2</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="11">
         <v>4.4817745944661404E-3</v>
       </c>
-      <c r="T6" s="12">
+      <c r="T6" s="11">
         <v>8.8557362285307604E-4</v>
       </c>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>-3.8396379118492401E-3</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <v>1.77354633563962E-3</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="11">
         <v>8.6156600053839301E-3</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="13">
         <v>1.49694992296447E-2</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="Q7" s="19" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="Q7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="R7" s="12">
+      <c r="R7" s="11">
         <v>1.87890598317693E-3</v>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="11">
         <v>2.1335396957707299E-3</v>
       </c>
-      <c r="T7" s="12">
+      <c r="T7" s="13">
         <v>2.2148566141028898E-2</v>
       </c>
-      <c r="U7" s="12">
+      <c r="U7" s="13">
         <v>1.8240027753454201E-2</v>
       </c>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AH7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <v>2.4667389372653802E-2</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="13">
         <v>1.8598626895833199E-2</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="13">
         <v>3.17229528512031E-2</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="13">
         <v>2.82295809814362E-2</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="13">
         <v>2.8630475631416699E-2</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="Q8" s="19" t="s">
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="Q8" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="R8" s="12">
+      <c r="R8" s="13">
         <v>2.1826150126815502E-2</v>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="13">
         <v>3.5570069071712701E-2</v>
       </c>
-      <c r="T8" s="12">
+      <c r="T8" s="13">
         <v>5.70740843528953E-2</v>
       </c>
-      <c r="U8" s="12">
+      <c r="U8" s="13">
         <v>4.9917932160085401E-2</v>
       </c>
-      <c r="V8" s="12">
+      <c r="V8" s="13">
         <v>2.6516233995892501E-2</v>
       </c>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
-      <c r="AG8" s="13"/>
-      <c r="AH8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>2.10780704016208E-3</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="13">
         <v>6.3319611654049698E-3</v>
       </c>
-      <c r="D9" s="12">
-        <v>-1.0955434681696101E-2</v>
-      </c>
-      <c r="E9" s="12">
-        <v>-1.4975427465528801E-2</v>
-      </c>
-      <c r="F9" s="16">
+      <c r="D9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="13">
         <v>8.8786954886132807E-3</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="13">
         <v>2.4436907525473599E-2</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="Q9" s="19" t="s">
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="Q9" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="13">
         <v>1.9787760627790099E-2</v>
       </c>
-      <c r="S9" s="12">
+      <c r="S9" s="13">
         <v>6.63938062652418E-3</v>
       </c>
-      <c r="T9" s="12">
-        <v>-8.3495792001338394E-3</v>
-      </c>
-      <c r="U9" s="12">
-        <v>-8.7077958130875703E-3</v>
-      </c>
-      <c r="V9" s="12">
+      <c r="T9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="V9" s="13">
         <v>2.0686555951441601E-2</v>
       </c>
-      <c r="W9" s="12">
+      <c r="W9" s="13">
         <v>5.2550797516533201E-2</v>
       </c>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
-      <c r="AH9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="16">
-        <v>-1.4893089406173499E-2</v>
-      </c>
-      <c r="C10" s="12">
+      <c r="B10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="11">
         <v>2.85819527083779E-4</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="11">
         <v>7.2858653033287396E-3</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="13">
         <v>1.1311045844285101E-2</v>
       </c>
-      <c r="F10" s="16">
-        <v>-1.25022219873272E-2</v>
-      </c>
-      <c r="G10" s="16">
-        <v>8.9277918780134094E-3</v>
-      </c>
-      <c r="H10" s="16">
+      <c r="F10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="13">
         <v>6.1020223278046397E-3</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="Q10" s="19" t="s">
+      <c r="I10" s="13"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="Q10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="R10" s="12">
-        <v>-8.3658578027370999E-3</v>
-      </c>
-      <c r="S10" s="12">
+      <c r="R10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="S10" s="11">
         <v>2.2513984635190599E-3</v>
       </c>
-      <c r="T10" s="12">
+      <c r="T10" s="13">
         <v>2.0647681530669201E-2</v>
       </c>
-      <c r="U10" s="12">
+      <c r="U10" s="13">
         <v>1.7225208129436499E-2</v>
       </c>
-      <c r="V10" s="12">
-        <v>-8.2963898180716898E-3</v>
-      </c>
-      <c r="W10" s="12">
-        <v>1.2061315249409101E-2</v>
-      </c>
-      <c r="X10" s="12">
+      <c r="V10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="W10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="X10" s="13">
         <v>1.9286990892640899E-2</v>
       </c>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="13"/>
-      <c r="AF10" s="13"/>
-      <c r="AG10" s="13"/>
-      <c r="AH10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="14"/>
+      <c r="AF10" s="14"/>
+      <c r="AG10" s="14"/>
+      <c r="AH10" s="14"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="14">
         <v>5.6214718084875603E-2</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>4.0003190129693E-2</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="14">
         <v>5.14616869493933E-2</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="14">
         <v>4.3457417185580001E-2</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="14">
         <v>4.72779287967778E-2</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="14">
         <v>5.7282720215539699E-2</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="14">
         <v>4.0844952581908602E-2</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="14">
         <v>4.5578325526731897E-2</v>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
       <c r="Q11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="13">
+      <c r="R11" s="14">
         <v>4.9222447302769499E-2</v>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="14">
         <v>5.0822665815146002E-2</v>
       </c>
-      <c r="T11" s="13">
+      <c r="T11" s="14">
         <v>5.8563963998175601E-2</v>
       </c>
-      <c r="U11" s="13">
+      <c r="U11" s="14">
         <v>6.5812952347766907E-2</v>
       </c>
-      <c r="V11" s="13">
+      <c r="V11" s="14">
         <v>4.5067588766296997E-2</v>
       </c>
-      <c r="W11" s="13">
+      <c r="W11" s="14">
         <v>6.5312446024176504E-2</v>
       </c>
-      <c r="X11" s="13">
+      <c r="X11" s="14">
         <v>6.1272887673672602E-2</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="Y11" s="14">
         <v>4.2990065004908103E-2</v>
       </c>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
-      <c r="AH11" s="13"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="14"/>
+      <c r="AF11" s="14"/>
+      <c r="AG11" s="14"/>
+      <c r="AH11" s="14"/>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="14">
         <v>6.1673494405777102E-2</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="14">
         <v>5.0054582140548601E-2</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="14">
         <v>6.2385988821183701E-2</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="14">
         <v>4.75880723725359E-2</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="14">
         <v>5.7122909627042501E-2</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="14">
         <v>5.9641319556728398E-2</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="14">
         <v>4.73076493095042E-2</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="14">
         <v>5.3053954756444997E-2</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="14">
         <v>1.83962565451125E-2</v>
       </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
       <c r="Q12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R12" s="13">
+      <c r="R12" s="14">
         <v>8.5300030369382607E-2</v>
       </c>
-      <c r="S12" s="13">
+      <c r="S12" s="14">
         <v>8.4829585159443305E-2</v>
       </c>
-      <c r="T12" s="13">
+      <c r="T12" s="14">
         <v>8.8366803534051297E-2</v>
       </c>
-      <c r="U12" s="13">
+      <c r="U12" s="14">
         <v>8.7224669395878598E-2</v>
       </c>
-      <c r="V12" s="13">
+      <c r="V12" s="14">
         <v>8.6565717225956504E-2</v>
       </c>
-      <c r="W12" s="13">
+      <c r="W12" s="14">
         <v>0.108525331498439</v>
       </c>
-      <c r="X12" s="13">
+      <c r="X12" s="14">
         <v>8.41967727018329E-2</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Y12" s="14">
         <v>7.9228129926254706E-2</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="Z12" s="14">
         <v>5.5901912083008098E-2</v>
       </c>
-      <c r="AA12" s="13"/>
-      <c r="AB12" s="13"/>
-      <c r="AC12" s="13"/>
-      <c r="AD12" s="13"/>
-      <c r="AE12" s="13"/>
-      <c r="AF12" s="13"/>
-      <c r="AG12" s="13"/>
-      <c r="AH12" s="13"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="14"/>
+      <c r="AF12" s="14"/>
+      <c r="AG12" s="14"/>
+      <c r="AH12" s="14"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="14">
         <v>2.9744134737838102E-2</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="14">
         <v>2.5818107062192602E-2</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="14">
         <v>2.2805578834935902E-2</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="14">
         <v>3.89083076723283E-2</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="14">
         <v>2.6555786432994801E-2</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="14">
         <v>6.6943325190307795E-2</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="14">
         <v>2.8486277422519201E-2</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="14">
         <v>2.9093225956209001E-2</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="14">
         <v>6.2822655119190093E-2</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="14">
         <v>6.8808473279646606E-2</v>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
       <c r="Q13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="R13" s="13">
+      <c r="R13" s="14">
         <v>3.86872057129539E-2</v>
       </c>
-      <c r="S13" s="13">
+      <c r="S13" s="14">
         <v>4.40827884548693E-2</v>
       </c>
-      <c r="T13" s="13">
+      <c r="T13" s="14">
         <v>5.0498897274600801E-2</v>
       </c>
-      <c r="U13" s="13">
+      <c r="U13" s="14">
         <v>5.8193994141083602E-2</v>
       </c>
-      <c r="V13" s="13">
+      <c r="V13" s="14">
         <v>3.6972911703707499E-2</v>
       </c>
-      <c r="W13" s="13">
+      <c r="W13" s="14">
         <v>5.62710437977616E-2</v>
       </c>
-      <c r="X13" s="13">
+      <c r="X13" s="14">
         <v>5.3984091281068403E-2</v>
       </c>
-      <c r="Y13" s="13">
+      <c r="Y13" s="14">
         <v>3.4625574673583397E-2</v>
       </c>
-      <c r="Z13" s="13">
+      <c r="Z13" s="14">
         <v>1.1701725522731301E-2</v>
       </c>
-      <c r="AA13" s="13">
+      <c r="AA13" s="14">
         <v>5.6869990844019697E-2</v>
       </c>
-      <c r="AB13" s="13"/>
-      <c r="AC13" s="13"/>
-      <c r="AD13" s="13"/>
-      <c r="AE13" s="13"/>
-      <c r="AF13" s="13"/>
-      <c r="AG13" s="13"/>
-      <c r="AH13" s="13"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="14"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="14"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="14">
         <v>8.2237755410579802E-2</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="14">
         <v>7.9498576619338096E-2</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="14">
         <v>0.10322467295139801</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="14">
         <v>8.9030100528793399E-2</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="14">
         <v>7.8809680223538806E-2</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="14">
         <v>7.6851487326127801E-2</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="14">
         <v>8.8231853770265503E-2</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="14">
         <v>7.3704286878066599E-2</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="14">
         <v>0.108800901165783</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="14">
         <v>0.11874932296794</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="14">
         <v>9.8505792480880594E-2</v>
       </c>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
       <c r="Q14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R14" s="13">
+      <c r="R14" s="14">
         <v>5.2158876953093701E-2</v>
       </c>
-      <c r="S14" s="13">
+      <c r="S14" s="14">
         <v>5.9486314698353998E-2</v>
       </c>
-      <c r="T14" s="13">
+      <c r="T14" s="14">
         <v>6.8434346276778704E-2</v>
       </c>
-      <c r="U14" s="13">
+      <c r="U14" s="14">
         <v>6.8491734028022E-2</v>
       </c>
-      <c r="V14" s="13">
+      <c r="V14" s="14">
         <v>5.2068499021431E-2</v>
       </c>
-      <c r="W14" s="13">
+      <c r="W14" s="14">
         <v>7.6097548518572394E-2</v>
       </c>
-      <c r="X14" s="13">
+      <c r="X14" s="14">
         <v>6.7171465542200298E-2</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="Y14" s="14">
         <v>4.88154332729041E-2</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="Z14" s="14">
         <v>3.6746678541143198E-2</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AA14" s="14">
         <v>7.7738955452256606E-2</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AB14" s="14">
         <v>2.6960203346527298E-2</v>
       </c>
-      <c r="AC14" s="13"/>
-      <c r="AD14" s="13"/>
-      <c r="AE14" s="13"/>
-      <c r="AF14" s="13"/>
-      <c r="AG14" s="13"/>
-      <c r="AH14" s="13"/>
+      <c r="AC14" s="14"/>
+      <c r="AD14" s="14"/>
+      <c r="AE14" s="14"/>
+      <c r="AF14" s="14"/>
+      <c r="AG14" s="14"/>
+      <c r="AH14" s="14"/>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="14">
         <v>0.16686610304142799</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="14">
         <v>0.16303358621355901</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="14">
         <v>0.17301096135973701</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="14">
         <v>0.17941833962687101</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="14">
         <v>0.134846454850921</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="14">
         <v>0.197365389046778</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="14">
         <v>0.169620493200624</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="14">
         <v>0.14323658756222199</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="14">
         <v>0.21078214910607099</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="14">
         <v>0.20522754603791099</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="14">
         <v>0.16890054493624501</v>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="14">
         <v>0.195348581699372</v>
       </c>
-      <c r="N15" s="17"/>
+      <c r="N15" s="14"/>
       <c r="Q15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="R15" s="13">
+      <c r="R15" s="14">
         <v>5.3988005798518403E-2</v>
       </c>
-      <c r="S15" s="13">
+      <c r="S15" s="14">
         <v>5.9727853509050702E-2</v>
       </c>
-      <c r="T15" s="13">
+      <c r="T15" s="14">
         <v>6.2715918166892301E-2</v>
       </c>
-      <c r="U15" s="13">
+      <c r="U15" s="14">
         <v>6.8316953747518394E-2</v>
       </c>
-      <c r="V15" s="13">
+      <c r="V15" s="14">
         <v>5.3402250825701603E-2</v>
       </c>
-      <c r="W15" s="13">
+      <c r="W15" s="14">
         <v>7.7937686319100599E-2</v>
       </c>
-      <c r="X15" s="13">
+      <c r="X15" s="14">
         <v>6.46489441233698E-2</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="Y15" s="14">
         <v>5.04501977408775E-2</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="Z15" s="14">
         <v>2.9617176680629399E-2</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AA15" s="14">
         <v>6.9446652668598896E-2</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AB15" s="14">
         <v>2.1590612451292599E-2</v>
       </c>
-      <c r="AC15" s="13">
+      <c r="AC15" s="14">
         <v>4.5343152808564699E-2</v>
       </c>
-      <c r="AD15" s="13"/>
-      <c r="AE15" s="13"/>
-      <c r="AF15" s="13"/>
-      <c r="AG15" s="13"/>
-      <c r="AH15" s="13"/>
+      <c r="AD15" s="14"/>
+      <c r="AE15" s="14"/>
+      <c r="AF15" s="14"/>
+      <c r="AG15" s="14"/>
+      <c r="AH15" s="14"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="15">
         <v>9.1318964013764603E-2</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="15">
         <v>0.10544881471138801</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="15">
         <v>0.111665516369056</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="15">
         <v>0.133351759780094</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="15">
         <v>7.7525283777430107E-2</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="15">
         <v>0.12593586058791201</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="15">
         <v>0.122837139571433</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="15">
         <v>8.5581430877093995E-2</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="15">
         <v>0.17173023326817299</v>
       </c>
-      <c r="K16" s="18">
+      <c r="K16" s="15">
         <v>0.16925947889590601</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="15">
         <v>0.12912064875798199</v>
       </c>
-      <c r="M16" s="18">
+      <c r="M16" s="15">
         <v>0.14671241956386999</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="15">
         <v>0.153508947666294</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R16" s="13">
+      <c r="R16" s="14">
         <v>5.4221429975235602E-2</v>
       </c>
-      <c r="S16" s="13">
+      <c r="S16" s="14">
         <v>5.1167511786188502E-2</v>
       </c>
-      <c r="T16" s="13">
+      <c r="T16" s="14">
         <v>6.7479957139225596E-2</v>
       </c>
-      <c r="U16" s="13">
+      <c r="U16" s="14">
         <v>6.4741301351457906E-2</v>
       </c>
-      <c r="V16" s="13">
+      <c r="V16" s="14">
         <v>3.6434444957582697E-2</v>
       </c>
-      <c r="W16" s="13">
+      <c r="W16" s="14">
         <v>8.2303855647378396E-2</v>
       </c>
-      <c r="X16" s="13">
+      <c r="X16" s="14">
         <v>6.5761307273554101E-2</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Y16" s="14">
         <v>4.2531737995805598E-2</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="Z16" s="14">
         <v>5.3747581537369103E-2</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AA16" s="14">
         <v>0.111527647467109</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AB16" s="14">
         <v>4.2920544910553297E-2</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AC16" s="14">
         <v>6.3090140316232501E-2</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AD16" s="14">
         <v>7.4538043733467299E-2</v>
       </c>
-      <c r="AE16" s="13"/>
-      <c r="AF16" s="13"/>
-      <c r="AG16" s="13"/>
-      <c r="AH16" s="13"/>
+      <c r="AE16" s="14"/>
+      <c r="AF16" s="14"/>
+      <c r="AG16" s="14"/>
+      <c r="AH16" s="14"/>
     </row>
     <row r="17" spans="17:34" x14ac:dyDescent="0.3">
       <c r="Q17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="13">
+      <c r="R17" s="14">
         <v>7.0772891882266403E-2</v>
       </c>
-      <c r="S17" s="13">
+      <c r="S17" s="14">
         <v>5.4719939251788897E-2</v>
       </c>
-      <c r="T17" s="13">
+      <c r="T17" s="14">
         <v>6.7126885926402605E-2</v>
       </c>
-      <c r="U17" s="13">
+      <c r="U17" s="14">
         <v>7.1407572710796896E-2</v>
       </c>
-      <c r="V17" s="13">
+      <c r="V17" s="14">
         <v>5.8795280456654803E-2</v>
       </c>
-      <c r="W17" s="13">
+      <c r="W17" s="14">
         <v>8.0818072944896596E-2</v>
       </c>
-      <c r="X17" s="13">
+      <c r="X17" s="14">
         <v>6.8186433952119305E-2</v>
       </c>
-      <c r="Y17" s="13">
+      <c r="Y17" s="14">
         <v>5.9301266205091803E-2</v>
       </c>
-      <c r="Z17" s="13">
+      <c r="Z17" s="14">
         <v>4.2218504332509198E-2</v>
       </c>
-      <c r="AA17" s="13">
+      <c r="AA17" s="14">
         <v>8.8485467003256393E-2</v>
       </c>
-      <c r="AB17" s="13">
+      <c r="AB17" s="14">
         <v>3.7377465089466801E-2</v>
       </c>
-      <c r="AC17" s="13">
+      <c r="AC17" s="14">
         <v>6.4277747849540906E-2</v>
       </c>
-      <c r="AD17" s="13">
+      <c r="AD17" s="14">
         <v>6.8356157725499495E-2</v>
       </c>
-      <c r="AE17" s="13">
+      <c r="AE17" s="14">
         <v>7.1898237216161107E-2</v>
       </c>
-      <c r="AF17" s="13"/>
-      <c r="AG17" s="13"/>
-      <c r="AH17" s="13"/>
+      <c r="AF17" s="14"/>
+      <c r="AG17" s="14"/>
+      <c r="AH17" s="14"/>
     </row>
     <row r="18" spans="17:34" x14ac:dyDescent="0.3">
       <c r="Q18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="R18" s="13">
+      <c r="R18" s="14">
         <v>8.5288883547778693E-2</v>
       </c>
-      <c r="S18" s="13">
+      <c r="S18" s="14">
         <v>9.1004295489332601E-2</v>
       </c>
-      <c r="T18" s="13">
+      <c r="T18" s="14">
         <v>0.10679920965110801</v>
       </c>
-      <c r="U18" s="13">
+      <c r="U18" s="14">
         <v>9.7628491828551101E-2</v>
       </c>
-      <c r="V18" s="13">
+      <c r="V18" s="14">
         <v>8.20494466529645E-2</v>
       </c>
-      <c r="W18" s="13">
+      <c r="W18" s="14">
         <v>0.11196786762642701</v>
       </c>
-      <c r="X18" s="13">
+      <c r="X18" s="14">
         <v>9.9945435433060101E-2</v>
       </c>
-      <c r="Y18" s="13">
+      <c r="Y18" s="14">
         <v>7.9656247255083606E-2</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="Z18" s="14">
         <v>0.12375468020052</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AA18" s="14">
         <v>0.14534200442633999</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AB18" s="14">
         <v>0.12670301894566099</v>
       </c>
-      <c r="AC18" s="13">
+      <c r="AC18" s="14">
         <v>0.132080991088983</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AD18" s="14">
         <v>0.13503848023037501</v>
       </c>
-      <c r="AE18" s="13">
+      <c r="AE18" s="14">
         <v>0.12741606620351401</v>
       </c>
-      <c r="AF18" s="13">
+      <c r="AF18" s="14">
         <v>0.14530511471669599</v>
       </c>
-      <c r="AG18" s="13"/>
-      <c r="AH18" s="13"/>
+      <c r="AG18" s="14"/>
+      <c r="AH18" s="14"/>
     </row>
     <row r="19" spans="17:34" x14ac:dyDescent="0.3">
       <c r="Q19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="R19" s="13">
+      <c r="R19" s="14">
         <v>0.15889311547360199</v>
       </c>
-      <c r="S19" s="13">
+      <c r="S19" s="14">
         <v>0.16264606546440799</v>
       </c>
-      <c r="T19" s="13">
+      <c r="T19" s="14">
         <v>0.190036022446914</v>
       </c>
-      <c r="U19" s="13">
+      <c r="U19" s="14">
         <v>0.177706824534899</v>
       </c>
-      <c r="V19" s="13">
+      <c r="V19" s="14">
         <v>0.135227066373282</v>
       </c>
-      <c r="W19" s="13">
+      <c r="W19" s="14">
         <v>0.220211368569591</v>
       </c>
-      <c r="X19" s="13">
+      <c r="X19" s="14">
         <v>0.180912977163871</v>
       </c>
-      <c r="Y19" s="13">
+      <c r="Y19" s="14">
         <v>0.142868440290597</v>
       </c>
-      <c r="Z19" s="13">
+      <c r="Z19" s="14">
         <v>0.21921634877721299</v>
       </c>
-      <c r="AA19" s="13">
+      <c r="AA19" s="14">
         <v>0.26900468695437701</v>
       </c>
-      <c r="AB19" s="13">
+      <c r="AB19" s="14">
         <v>0.21672627042268799</v>
       </c>
-      <c r="AC19" s="13">
+      <c r="AC19" s="14">
         <v>0.20766948463276999</v>
       </c>
-      <c r="AD19" s="13">
+      <c r="AD19" s="14">
         <v>0.212575895507817</v>
       </c>
-      <c r="AE19" s="13">
+      <c r="AE19" s="14">
         <v>0.192767207162865</v>
       </c>
-      <c r="AF19" s="13">
+      <c r="AF19" s="14">
         <v>0.21449379119614401</v>
       </c>
-      <c r="AG19" s="13">
+      <c r="AG19" s="14">
         <v>0.204960775076722</v>
       </c>
-      <c r="AH19" s="13"/>
+      <c r="AH19" s="14"/>
     </row>
     <row r="20" spans="17:34" x14ac:dyDescent="0.3">
-      <c r="Q20" s="20" t="s">
+      <c r="Q20" s="17" t="s">
         <v>6</v>
       </c>
       <c r="R20" s="15">
